--- a/timetable_generator/timetable_outputs/CSE_Sem3_SectionA_Timetable.xlsx
+++ b/timetable_generator/timetable_outputs/CSE_Sem3_SectionA_Timetable.xlsx
@@ -467,22 +467,36 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CA262
+Software design tools and tehniques
+C101
+Dr. Sunil P V</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS263
-Design and analysis of algorithm 
-C101
-Dr. Malay </t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+          <t>CA262
+Software design tools and tehniques
+C101
+Dr. Sunil P V</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>CS261
 Operating Sytems
 C101
 Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CS264
+Computer networks 
+C101
+Dr. Prabhu Prasad</t>
         </is>
       </c>
     </row>
@@ -494,10 +508,10 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CS261
-Operating Sytems
-C101
-Dr. Suvadip Hazra</t>
+          <t>CS264
+Computer networks 
+C101
+Dr. Prabhu Prasad</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,22 +523,8 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS263
-Design and analysis of algorithm 
-C101
-Dr. Malay </t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CS264
-Computer networks 
-C101
-Dr. Prabhu Prasad</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -532,13 +532,20 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS263
+Design and analysis of algorithm 
+C101
+Dr. Malay </t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CA262
-Software design tools and tehniques
-C101
-Dr. Sunil P V</t>
+          <t>CS261
+Operating Sytems
+C101
+Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -551,14 +558,7 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CA262
-Software design tools and tehniques
-C101
-Dr. Sunil P V</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -570,22 +570,23 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CS263
+Design and analysis of algorithm 
+C101
+Dr. Malay </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>CS264
 Computer networks 
 C101
-Dr. Prabhu Prasad</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CS264
-Computer networks 
-C101
-Dr. Prabhu Prasad</t>
+Dr. Prabhu Prasad
+[TUTORIAL]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
